--- a/manufacturing-process-capability-analysis/Data/Manufacturing_Quality_Project_Dataset.xlsx
+++ b/manufacturing-process-capability-analysis/Data/Manufacturing_Quality_Project_Dataset.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ajudn\OneDrive\Desktop\manufacturing-process-capability-analysis\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F99BD33D-436D-4A04-8DBA-1BDF9A6631DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB00AE1F-CB4E-43EA-999D-C1F9D253676C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
